--- a/產學_每師平均產學收入.xlsx
+++ b/產學_每師平均產學收入.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\喬文作業區\115\115  校務研究\115 名稱及課程相似系所比較分析\系所雷同比較Raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\喬文作業區\115\115  校務研究\115 名稱及課程相似系所比較分析\比較分析網站\comparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A307376D-5482-48F9-88FF-62A463ADDA54}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819A0C01-4B2B-4058-A6BA-AC9E4B80B946}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="79">
   <si>
     <t>學院</t>
   </si>
@@ -263,14 +263,14 @@
   <si>
     <t>電腦與通訊工程系</t>
   </si>
-  <si>
-    <t>2018-2025 專任教師平均</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -314,10 +314,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -9929,998 +9932,968 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14762DCB-5661-465B-B92B-27F6CE74DB64}">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.77734375" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="4"/>
+    <col min="10" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="1">
+      <c r="C2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="3">
         <v>170000</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="3">
         <v>11</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="3">
         <v>15454.5454545455</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="C3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="3">
         <v>395000</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="3">
         <v>13</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="3">
         <v>30384.615384615401</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="3">
         <v>75000</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="3">
         <v>14</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="3">
         <v>5357.1428571428596</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="C5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="3">
         <v>422224</v>
       </c>
-      <c r="F5" s="1">
-        <v>12</v>
-      </c>
-      <c r="G5" s="1">
+      <c r="F5" s="3">
+        <v>12</v>
+      </c>
+      <c r="G5" s="3">
         <v>35185.333333333299</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="C6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="3">
         <v>210000</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="3">
         <v>13</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="3">
         <v>16153.8461538462</v>
       </c>
-      <c r="H6" s="1">
-        <f>AVERAGE(F2:F6)</f>
-        <v>12.6</v>
-      </c>
+      <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="C7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="3">
         <v>3110000</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="3">
         <v>13</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="3">
         <v>239230.76923076899</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="C8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="3">
         <v>18845000</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="3">
         <v>11</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="3">
         <v>1713181.81818182</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="C9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="3">
         <v>5925000</v>
       </c>
-      <c r="F9" s="1">
-        <v>12</v>
-      </c>
-      <c r="G9" s="1">
+      <c r="F9" s="3">
+        <v>12</v>
+      </c>
+      <c r="G9" s="3">
         <v>493750</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="C10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="3">
         <v>4600000</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="3">
         <v>13</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="3">
         <v>353846.15384615399</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="1" t="s">
+      <c r="C11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="3">
         <v>2833000</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="3">
         <v>13</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="3">
         <v>217923.07692307699</v>
       </c>
-      <c r="H11">
-        <f>AVERAGE(F7:F11)</f>
-        <v>12.4</v>
-      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="1">
+      <c r="C12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="3">
         <v>4973640</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="3">
         <v>26</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" s="3">
         <v>191293.84615384601</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="C13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="3">
         <v>20943416</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="3">
         <v>25</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="3">
         <v>837736.64</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="C14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="3">
         <v>14545800</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="3">
         <v>28</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="3">
         <v>519492.85714285698</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="C15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="3">
         <v>19984400</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="3">
         <v>29</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="3">
         <v>689117.24137931003</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D16" s="1" t="s">
+      <c r="C16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="3">
         <v>20559214</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="3">
         <v>30</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="3">
         <v>685307.13333333295</v>
       </c>
-      <c r="H16">
-        <f>AVERAGE(F12:F16)</f>
-        <v>27.6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="1">
+      <c r="C17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="3">
         <v>112322409</v>
       </c>
-      <c r="F17" s="1">
-        <v>12</v>
-      </c>
-      <c r="G17" s="1">
+      <c r="F17" s="3">
+        <v>12</v>
+      </c>
+      <c r="G17" s="3">
         <v>9360200.75</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D18" s="1" t="s">
+      <c r="C18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="3">
         <v>103006598</v>
       </c>
-      <c r="F18" s="1">
-        <v>12</v>
-      </c>
-      <c r="G18" s="1">
+      <c r="F18" s="3">
+        <v>12</v>
+      </c>
+      <c r="G18" s="3">
         <v>8583883.1666666698</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D19" s="1" t="s">
+      <c r="C19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="3">
         <v>89319647</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="3">
         <v>13</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" s="3">
         <v>6870742.0769230798</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D20" s="1" t="s">
+      <c r="C20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="3">
         <v>87469550</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="3">
         <v>13</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" s="3">
         <v>6728426.9230769202</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D21" s="2" t="s">
+      <c r="C21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="3">
         <v>679587664</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="3">
         <v>11</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21" s="3">
         <v>61780696.727272697</v>
       </c>
-      <c r="H21">
-        <f>AVERAGE(F17:F21)</f>
-        <v>12.2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="1">
+      <c r="C22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="3">
         <v>2369000</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="3">
         <v>11</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22" s="3">
         <v>215363.636363636</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D23" s="1" t="s">
+      <c r="C23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="3">
         <v>1440000</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="3">
         <v>10</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G23" s="3">
         <v>144000</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D24" s="1" t="s">
+      <c r="C24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" s="3">
         <v>1946348</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="3">
         <v>9</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G24" s="3">
         <v>216260.88888888899</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D25" s="1" t="s">
+      <c r="C25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" s="3">
         <v>1594000</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="3">
         <v>9</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G25" s="3">
         <v>177111.11111111101</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D26" s="1" t="s">
+      <c r="C26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26" s="3">
         <v>36000</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="3">
         <v>10</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G26" s="3">
         <v>3600</v>
       </c>
-      <c r="H26">
-        <f>AVERAGE(F22:F26)</f>
-        <v>9.8000000000000007</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" s="1">
+      <c r="C27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" s="3">
         <v>430000</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="3">
         <v>13</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G27" s="3">
         <v>33076.9230769231</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" s="1" t="s">
+      <c r="C28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E28" s="3">
         <v>514731</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="3">
         <v>13</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G28" s="3">
         <v>39594.692307692298</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D29" s="1" t="s">
+      <c r="C29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29" s="3">
         <v>91191</v>
       </c>
-      <c r="F29" s="1">
-        <v>12</v>
-      </c>
-      <c r="G29" s="1">
+      <c r="F29" s="3">
+        <v>12</v>
+      </c>
+      <c r="G29" s="3">
         <v>7599.25</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D30" s="1" t="s">
+      <c r="C30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30" s="3">
         <v>111520</v>
       </c>
-      <c r="F30" s="1">
-        <v>12</v>
-      </c>
-      <c r="G30" s="1">
+      <c r="F30" s="3">
+        <v>12</v>
+      </c>
+      <c r="G30" s="3">
         <v>9293.3333333333303</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D31" s="1" t="s">
+      <c r="C31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E31" s="3">
         <v>796005</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="3">
         <v>11</v>
       </c>
-      <c r="G31" s="1">
+      <c r="G31" s="3">
         <v>72364.090909090897</v>
       </c>
-      <c r="H31">
-        <f>AVERAGE(F27:F31)</f>
-        <v>12.2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" s="1">
+      <c r="C32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" s="3">
         <v>7972183</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="3">
         <v>15</v>
       </c>
-      <c r="G32" s="1">
+      <c r="G32" s="3">
         <v>531478.86666666705</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D33" s="1" t="s">
+      <c r="C33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33" s="3">
         <v>600000</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="3">
         <v>15</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G33" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D34" s="1" t="s">
+      <c r="C34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34" s="3">
         <v>2000000</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34" s="3">
         <v>16</v>
       </c>
-      <c r="G34" s="1">
+      <c r="G34" s="3">
         <v>125000</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D35" s="1" t="s">
+      <c r="C35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35" s="3">
         <v>1250000</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35" s="3">
         <v>17</v>
       </c>
-      <c r="G35" s="1">
+      <c r="G35" s="3">
         <v>73529.411764705903</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D36" s="1" t="s">
+      <c r="C36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36" s="3">
         <v>1490000</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36" s="3">
         <v>16</v>
       </c>
-      <c r="G36" s="1">
+      <c r="G36" s="3">
         <v>93125</v>
       </c>
-      <c r="H36">
-        <f>AVERAGE(F32:F36)</f>
-        <v>15.8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37" s="1">
+      <c r="C37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="3">
         <v>455000</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37" s="3">
         <v>16</v>
       </c>
-      <c r="G37" s="1">
+      <c r="G37" s="3">
         <v>28437.5</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D38" s="1" t="s">
+      <c r="C38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E38" s="3">
         <v>495000</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38" s="3">
         <v>15</v>
       </c>
-      <c r="G38" s="1">
+      <c r="G38" s="3">
         <v>33000</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D39" s="1" t="s">
+      <c r="C39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E39" s="3">
         <v>500000</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="3">
         <v>14</v>
       </c>
-      <c r="G39" s="1">
+      <c r="G39" s="3">
         <v>35714.285714285703</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D40" s="1" t="s">
+      <c r="C40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E40" s="3">
         <v>565000</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40" s="3">
         <v>15</v>
       </c>
-      <c r="G40" s="1">
+      <c r="G40" s="3">
         <v>37666.666666666701</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D41" s="1" t="s">
+      <c r="C41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E41" s="3">
         <v>1975500</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41" s="3">
         <v>15</v>
       </c>
-      <c r="G41" s="1">
+      <c r="G41" s="3">
         <v>131700</v>
-      </c>
-      <c r="H41">
-        <f>AVERAGE(F37:F41)</f>
-        <v>15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/產學_每師平均產學收入.xlsx
+++ b/產學_每師平均產學收入.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\喬文作業區\115\115  校務研究\115 名稱及課程相似系所比較分析\比較分析網站\comparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819A0C01-4B2B-4058-A6BA-AC9E4B80B946}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE67853C-4EBD-4B0A-B8D3-6C95C0282E85}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TableData" sheetId="1" r:id="rId1"/>
@@ -659,7 +659,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G402"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -694,7 +693,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -717,7 +716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -740,7 +739,7 @@
         <v>8333.3333333333303</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -763,7 +762,7 @@
         <v>12666.333333333299</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -786,7 +785,7 @@
         <v>40500</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,7 +808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -832,7 +831,7 @@
         <v>124750</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -855,7 +854,7 @@
         <v>127272.727272727</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,7 +877,7 @@
         <v>103000</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -901,7 +900,7 @@
         <v>102919.222222222</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
@@ -924,7 +923,7 @@
         <v>54500</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -947,7 +946,7 @@
         <v>161422.22222222199</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
@@ -970,7 +969,7 @@
         <v>191316.66666666701</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -993,7 +992,7 @@
         <v>77137.777777777796</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
@@ -1016,7 +1015,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -1039,7 +1038,7 @@
         <v>2324319.63636364</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -1062,7 +1061,7 @@
         <v>949236.363636364</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>20</v>
       </c>
@@ -1085,7 +1084,7 @@
         <v>53800</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
@@ -1108,7 +1107,7 @@
         <v>299944.375</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>20</v>
       </c>
@@ -1131,7 +1130,7 @@
         <v>78733.75</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -1154,7 +1153,7 @@
         <v>60774.733333333301</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
@@ -1177,7 +1176,7 @@
         <v>38117.647058823502</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>20</v>
       </c>
@@ -1200,7 +1199,7 @@
         <v>64752.611111111102</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>20</v>
       </c>
@@ -1223,7 +1222,7 @@
         <v>267137.64705882402</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1430,7 +1429,7 @@
         <v>131700</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>20</v>
       </c>
@@ -1453,7 +1452,7 @@
         <v>6600</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>20</v>
       </c>
@@ -1476,7 +1475,7 @@
         <v>10909.090909090901</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,7 +1498,7 @@
         <v>234500</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>20</v>
       </c>
@@ -1522,7 +1521,7 @@
         <v>1709090.9090909101</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>20</v>
       </c>
@@ -1545,7 +1544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>20</v>
       </c>
@@ -1568,7 +1567,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>20</v>
       </c>
@@ -1591,7 +1590,7 @@
         <v>49000</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>20</v>
       </c>
@@ -1614,7 +1613,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>20</v>
       </c>
@@ -1637,7 +1636,7 @@
         <v>33333.333333333299</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>20</v>
       </c>
@@ -1660,7 +1659,7 @@
         <v>2391.9333333333302</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>20</v>
       </c>
@@ -1683,7 +1682,7 @@
         <v>56079.428571428602</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>20</v>
       </c>
@@ -1706,7 +1705,7 @@
         <v>33076.9230769231</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>20</v>
       </c>
@@ -1729,7 +1728,7 @@
         <v>39594.692307692298</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>20</v>
       </c>
@@ -1752,7 +1751,7 @@
         <v>7599.25</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>20</v>
       </c>
@@ -1775,7 +1774,7 @@
         <v>9293.3333333333303</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>20</v>
       </c>
@@ -1798,7 +1797,7 @@
         <v>72364.090909090897</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>20</v>
       </c>
@@ -1821,7 +1820,7 @@
         <v>69844.333333333299</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>20</v>
       </c>
@@ -1844,7 +1843,7 @@
         <v>105625</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>20</v>
       </c>
@@ -1867,7 +1866,7 @@
         <v>161666.66666666701</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>20</v>
       </c>
@@ -1890,7 +1889,7 @@
         <v>139269.5</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>20</v>
       </c>
@@ -1913,7 +1912,7 @@
         <v>741363.636363636</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>20</v>
       </c>
@@ -1936,7 +1935,7 @@
         <v>627500</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>20</v>
       </c>
@@ -1959,7 +1958,7 @@
         <v>541666.66666666698</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>20</v>
       </c>
@@ -1982,7 +1981,7 @@
         <v>577500</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>26</v>
       </c>
@@ -2005,7 +2004,7 @@
         <v>123339.090909091</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>26</v>
       </c>
@@ -2028,7 +2027,7 @@
         <v>243829.88888888899</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,7 +2050,7 @@
         <v>39080.5</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>26</v>
       </c>
@@ -2074,7 +2073,7 @@
         <v>59670.888888888898</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>26</v>
       </c>
@@ -2097,7 +2096,7 @@
         <v>19828.727272727301</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,7 +2119,7 @@
         <v>23218.272727272699</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>26</v>
       </c>
@@ -2143,7 +2142,7 @@
         <v>32889.727272727301</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>26</v>
       </c>
@@ -2166,7 +2165,7 @@
         <v>36275.090909090897</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>26</v>
       </c>
@@ -2189,7 +2188,7 @@
         <v>11875</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>26</v>
       </c>
@@ -2212,7 +2211,7 @@
         <v>59935.166666666701</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>26</v>
       </c>
@@ -2235,7 +2234,7 @@
         <v>743408.75</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>26</v>
       </c>
@@ -2258,7 +2257,7 @@
         <v>916.66666666666697</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>26</v>
       </c>
@@ -2281,7 +2280,7 @@
         <v>8666.6666666666697</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>26</v>
       </c>
@@ -2304,7 +2303,7 @@
         <v>6783.3333333333303</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>26</v>
       </c>
@@ -2327,7 +2326,7 @@
         <v>21538</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>26</v>
       </c>
@@ -2350,7 +2349,7 @@
         <v>41390.769230769198</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>26</v>
       </c>
@@ -2373,7 +2372,7 @@
         <v>107581.875</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>26</v>
       </c>
@@ -2396,7 +2395,7 @@
         <v>24946.9130434783</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>26</v>
       </c>
@@ -2419,7 +2418,7 @@
         <v>1323.65</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>26</v>
       </c>
@@ -2442,7 +2441,7 @@
         <v>48301.5</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>26</v>
       </c>
@@ -2465,7 +2464,7 @@
         <v>3880.5</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>26</v>
       </c>
@@ -2488,7 +2487,7 @@
         <v>20079.5454545455</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>26</v>
       </c>
@@ -2511,7 +2510,7 @@
         <v>58452.681818181802</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>26</v>
       </c>
@@ -2534,7 +2533,7 @@
         <v>5681.7142857142899</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>30</v>
       </c>
@@ -2557,7 +2556,7 @@
         <v>322059.34615384601</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>30</v>
       </c>
@@ -2580,7 +2579,7 @@
         <v>246357.15384615399</v>
       </c>
     </row>
-    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>30</v>
       </c>
@@ -2603,7 +2602,7 @@
         <v>226787.20000000001</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>30</v>
       </c>
@@ -2626,7 +2625,7 @@
         <v>162346.15384615399</v>
       </c>
     </row>
-    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>30</v>
       </c>
@@ -2649,7 +2648,7 @@
         <v>226208</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>30</v>
       </c>
@@ -2672,7 +2671,7 @@
         <v>308013.79166666698</v>
       </c>
     </row>
-    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>30</v>
       </c>
@@ -2695,7 +2694,7 @@
         <v>416145.83333333302</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>30</v>
       </c>
@@ -2718,7 +2717,7 @@
         <v>283062.08333333302</v>
       </c>
     </row>
-    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>30</v>
       </c>
@@ -2741,7 +2740,7 @@
         <v>833295.34615384601</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>30</v>
       </c>
@@ -2764,7 +2763,7 @@
         <v>846719.56</v>
       </c>
     </row>
-    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>30</v>
       </c>
@@ -2787,7 +2786,7 @@
         <v>863841.48</v>
       </c>
     </row>
-    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>30</v>
       </c>
@@ -2810,7 +2809,7 @@
         <v>567242.67857142899</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>30</v>
       </c>
@@ -2833,7 +2832,7 @@
         <v>1267069.4615384601</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>30</v>
       </c>
@@ -2856,7 +2855,7 @@
         <v>730505.77777777798</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>30</v>
       </c>
@@ -2879,7 +2878,7 @@
         <v>1119187.5</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>30</v>
       </c>
@@ -2902,7 +2901,7 @@
         <v>1097632.34615385</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>30</v>
       </c>
@@ -2925,7 +2924,7 @@
         <v>222062.5</v>
       </c>
     </row>
-    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>30</v>
       </c>
@@ -2948,7 +2947,7 @@
         <v>250956.764705882</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>30</v>
       </c>
@@ -2971,7 +2970,7 @@
         <v>344150.28571428597</v>
       </c>
     </row>
-    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>30</v>
       </c>
@@ -2994,7 +2993,7 @@
         <v>56666.666666666701</v>
       </c>
     </row>
-    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>30</v>
       </c>
@@ -3017,7 +3016,7 @@
         <v>134711.46666666699</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>30</v>
       </c>
@@ -3040,7 +3039,7 @@
         <v>604750</v>
       </c>
     </row>
-    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>30</v>
       </c>
@@ -3063,7 +3062,7 @@
         <v>447500</v>
       </c>
     </row>
-    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>30</v>
       </c>
@@ -3086,7 +3085,7 @@
         <v>1185285.7142857099</v>
       </c>
     </row>
-    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>30</v>
       </c>
@@ -3109,7 +3108,7 @@
         <v>591475.55555555597</v>
       </c>
     </row>
-    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>30</v>
       </c>
@@ -3132,7 +3131,7 @@
         <v>245800</v>
       </c>
     </row>
-    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>30</v>
       </c>
@@ -3155,7 +3154,7 @@
         <v>239815.555555556</v>
       </c>
     </row>
-    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>30</v>
       </c>
@@ -3178,7 +3177,7 @@
         <v>221995.555555556</v>
       </c>
     </row>
-    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>30</v>
       </c>
@@ -3201,7 +3200,7 @@
         <v>169580.555555556</v>
       </c>
     </row>
-    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>30</v>
       </c>
@@ -3224,7 +3223,7 @@
         <v>892910.11111111101</v>
       </c>
     </row>
-    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>30</v>
       </c>
@@ -3247,7 +3246,7 @@
         <v>1068865.6896551701</v>
       </c>
     </row>
-    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>30</v>
       </c>
@@ -3270,7 +3269,7 @@
         <v>1738547.4666666701</v>
       </c>
     </row>
-    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>30</v>
       </c>
@@ -3293,7 +3292,7 @@
         <v>1360161.2</v>
       </c>
     </row>
-    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>30</v>
       </c>
@@ -3316,7 +3315,7 @@
         <v>82063.448275862102</v>
       </c>
     </row>
-    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>30</v>
       </c>
@@ -3339,7 +3338,7 @@
         <v>214513.566666667</v>
       </c>
     </row>
-    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>30</v>
       </c>
@@ -3362,7 +3361,7 @@
         <v>2690096.9655172401</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>30</v>
       </c>
@@ -3385,7 +3384,7 @@
         <v>219340.25806451601</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>30</v>
       </c>
@@ -3408,7 +3407,7 @@
         <v>1238107.6521739101</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>30</v>
       </c>
@@ -3431,7 +3430,7 @@
         <v>1437089.82608696</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>30</v>
       </c>
@@ -3454,7 +3453,7 @@
         <v>1652690.4090909101</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>30</v>
       </c>
@@ -3477,7 +3476,7 @@
         <v>1475506.2727272699</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>30</v>
       </c>
@@ -3500,7 +3499,7 @@
         <v>484981</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>30</v>
       </c>
@@ -3523,7 +3522,7 @@
         <v>553571.31578947406</v>
       </c>
     </row>
-    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>30</v>
       </c>
@@ -3546,7 +3545,7 @@
         <v>987706.35294117697</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>30</v>
       </c>
@@ -3569,7 +3568,7 @@
         <v>969472.22222222202</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>30</v>
       </c>
@@ -3592,7 +3591,7 @@
         <v>1004418.6875</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>30</v>
       </c>
@@ -3615,7 +3614,7 @@
         <v>1055024.9375</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>30</v>
       </c>
@@ -3638,7 +3637,7 @@
         <v>879664.70588235301</v>
       </c>
     </row>
-    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>30</v>
       </c>
@@ -3661,7 +3660,7 @@
         <v>1086323.2777777801</v>
       </c>
     </row>
-    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>30</v>
       </c>
@@ -3684,7 +3683,7 @@
         <v>8463561.6086956505</v>
       </c>
     </row>
-    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>30</v>
       </c>
@@ -3707,7 +3706,7 @@
         <v>3048634.3181818202</v>
       </c>
     </row>
-    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>30</v>
       </c>
@@ -3730,7 +3729,7 @@
         <v>11143432.6818182</v>
       </c>
     </row>
-    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>30</v>
       </c>
@@ -3753,7 +3752,7 @@
         <v>4177613.57142857</v>
       </c>
     </row>
-    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>30</v>
       </c>
@@ -3776,7 +3775,7 @@
         <v>10066709.699999999</v>
       </c>
     </row>
-    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>30</v>
       </c>
@@ -3799,7 +3798,7 @@
         <v>3093707.63636364</v>
       </c>
     </row>
-    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>30</v>
       </c>
@@ -3822,7 +3821,7 @@
         <v>7142207.57142857</v>
       </c>
     </row>
-    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>30</v>
       </c>
@@ -3845,7 +3844,7 @@
         <v>10956158.0454545</v>
       </c>
     </row>
-    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>39</v>
       </c>
@@ -3868,7 +3867,7 @@
         <v>739517.96551724104</v>
       </c>
     </row>
-    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>39</v>
       </c>
@@ -3891,7 +3890,7 @@
         <v>1611829.86666667</v>
       </c>
     </row>
-    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>39</v>
       </c>
@@ -3914,7 +3913,7 @@
         <v>2389045.1612903201</v>
       </c>
     </row>
-    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>39</v>
       </c>
@@ -3937,7 +3936,7 @@
         <v>1508561.12903226</v>
       </c>
     </row>
-    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>39</v>
       </c>
@@ -3960,7 +3959,7 @@
         <v>390234.36666666699</v>
       </c>
     </row>
-    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>39</v>
       </c>
@@ -3983,7 +3982,7 @@
         <v>428081.65517241397</v>
       </c>
     </row>
-    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>39</v>
       </c>
@@ -4006,7 +4005,7 @@
         <v>321331.22222222202</v>
       </c>
     </row>
-    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>39</v>
       </c>
@@ -4029,7 +4028,7 @@
         <v>312203.03999999998</v>
       </c>
     </row>
-    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>39</v>
       </c>
@@ -4052,7 +4051,7 @@
         <v>1312138.9545454499</v>
       </c>
     </row>
-    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>39</v>
       </c>
@@ -4075,7 +4074,7 @@
         <v>1386726.75</v>
       </c>
     </row>
-    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>39</v>
       </c>
@@ -4098,7 +4097,7 @@
         <v>2352082.75</v>
       </c>
     </row>
-    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>39</v>
       </c>
@@ -4121,7 +4120,7 @@
         <v>2547669.4500000002</v>
       </c>
     </row>
-    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>39</v>
       </c>
@@ -4144,7 +4143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>39</v>
       </c>
@@ -4167,7 +4166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>39</v>
       </c>
@@ -4190,7 +4189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>41</v>
       </c>
@@ -4213,7 +4212,7 @@
         <v>440672.70588235301</v>
       </c>
     </row>
-    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>41</v>
       </c>
@@ -4236,7 +4235,7 @@
         <v>242672.77777777801</v>
       </c>
     </row>
-    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>41</v>
       </c>
@@ -4259,7 +4258,7 @@
         <v>472908</v>
       </c>
     </row>
-    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>41</v>
       </c>
@@ -4282,7 +4281,7 @@
         <v>480607.88235294097</v>
       </c>
     </row>
-    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>41</v>
       </c>
@@ -4305,7 +4304,7 @@
         <v>1179009.6470588199</v>
       </c>
     </row>
-    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>41</v>
       </c>
@@ -4328,7 +4327,7 @@
         <v>737890.63157894695</v>
       </c>
     </row>
-    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>41</v>
       </c>
@@ -4351,7 +4350,7 @@
         <v>1190735.45</v>
       </c>
     </row>
-    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>41</v>
       </c>
@@ -4374,7 +4373,7 @@
         <v>893445.3</v>
       </c>
     </row>
-    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>41</v>
       </c>
@@ -4397,7 +4396,7 @@
         <v>3449108.2666666699</v>
       </c>
     </row>
-    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>41</v>
       </c>
@@ -4420,7 +4419,7 @@
         <v>2638515.3125</v>
       </c>
     </row>
-    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>41</v>
       </c>
@@ -4443,7 +4442,7 @@
         <v>4972981.25</v>
       </c>
     </row>
-    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>41</v>
       </c>
@@ -4466,7 +4465,7 @@
         <v>1458437.5</v>
       </c>
     </row>
-    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>41</v>
       </c>
@@ -4489,7 +4488,7 @@
         <v>5250613.3333333302</v>
       </c>
     </row>
-    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>41</v>
       </c>
@@ -4512,7 +4511,7 @@
         <v>4137844.4705882398</v>
       </c>
     </row>
-    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>41</v>
       </c>
@@ -4535,7 +4534,7 @@
         <v>6513347.0588235296</v>
       </c>
     </row>
-    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>41</v>
       </c>
@@ -4558,7 +4557,7 @@
         <v>4820788.8</v>
       </c>
     </row>
-    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>41</v>
       </c>
@@ -4581,7 +4580,7 @@
         <v>6653332.4166666698</v>
       </c>
     </row>
-    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>41</v>
       </c>
@@ -4604,7 +4603,7 @@
         <v>6824919.9090909101</v>
       </c>
     </row>
-    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>41</v>
       </c>
@@ -4627,7 +4626,7 @@
         <v>4233857.0909090899</v>
       </c>
     </row>
-    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>41</v>
       </c>
@@ -4650,7 +4649,7 @@
         <v>9227013.7777777798</v>
       </c>
     </row>
-    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>41</v>
       </c>
@@ -4673,7 +4672,7 @@
         <v>14306502.5</v>
       </c>
     </row>
-    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>41</v>
       </c>
@@ -4696,7 +4695,7 @@
         <v>8268244.7272727303</v>
       </c>
     </row>
-    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>41</v>
       </c>
@@ -4719,7 +4718,7 @@
         <v>10076018.909090901</v>
       </c>
     </row>
-    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>41</v>
       </c>
@@ -4742,7 +4741,7 @@
         <v>8731262.0833333302</v>
       </c>
     </row>
-    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>41</v>
       </c>
@@ -4765,7 +4764,7 @@
         <v>88888.888888888905</v>
       </c>
     </row>
-    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>41</v>
       </c>
@@ -4788,7 +4787,7 @@
         <v>114444.444444444</v>
       </c>
     </row>
-    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>41</v>
       </c>
@@ -4811,7 +4810,7 @@
         <v>33333.333333333299</v>
       </c>
     </row>
-    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>41</v>
       </c>
@@ -4834,7 +4833,7 @@
         <v>22222.222222222201</v>
       </c>
     </row>
-    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>41</v>
       </c>
@@ -4857,7 +4856,7 @@
         <v>368777.77777777798</v>
       </c>
     </row>
-    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>41</v>
       </c>
@@ -4880,7 +4879,7 @@
         <v>402500</v>
       </c>
     </row>
-    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>41</v>
       </c>
@@ -4903,7 +4902,7 @@
         <v>382222.22222222202</v>
       </c>
     </row>
-    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>41</v>
       </c>
@@ -4926,7 +4925,7 @@
         <v>352122.22222222202</v>
       </c>
     </row>
-    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>41</v>
       </c>
@@ -4949,7 +4948,7 @@
         <v>192443.636363636</v>
       </c>
     </row>
-    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>41</v>
       </c>
@@ -4972,7 +4971,7 @@
         <v>5905.4545454545496</v>
       </c>
     </row>
-    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>41</v>
       </c>
@@ -4995,7 +4994,7 @@
         <v>575549.54545454495</v>
       </c>
     </row>
-    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>41</v>
       </c>
@@ -5018,7 +5017,7 @@
         <v>740058.181818182</v>
       </c>
     </row>
-    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>41</v>
       </c>
@@ -5041,7 +5040,7 @@
         <v>1442128.6</v>
       </c>
     </row>
-    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>41</v>
       </c>
@@ -5064,7 +5063,7 @@
         <v>1621617.5</v>
       </c>
     </row>
-    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>41</v>
       </c>
@@ -5087,7 +5086,7 @@
         <v>920069.83333333302</v>
       </c>
     </row>
-    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>41</v>
       </c>
@@ -5110,7 +5109,7 @@
         <v>3580628.1764705898</v>
       </c>
     </row>
-    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>48</v>
       </c>
@@ -5133,7 +5132,7 @@
         <v>135866.66666666701</v>
       </c>
     </row>
-    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>48</v>
       </c>
@@ -5156,7 +5155,7 @@
         <v>74200</v>
       </c>
     </row>
-    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>48</v>
       </c>
@@ -5179,7 +5178,7 @@
         <v>602528</v>
       </c>
     </row>
-    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>48</v>
       </c>
@@ -5202,7 +5201,7 @@
         <v>227685</v>
       </c>
     </row>
-    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
         <v>48</v>
       </c>
@@ -5225,7 +5224,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>48</v>
       </c>
@@ -5248,7 +5247,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>48</v>
       </c>
@@ -5271,7 +5270,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>48</v>
       </c>
@@ -5294,7 +5293,7 @@
         <v>75800</v>
       </c>
     </row>
-    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>48</v>
       </c>
@@ -5317,7 +5316,7 @@
         <v>220875</v>
       </c>
     </row>
-    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>48</v>
       </c>
@@ -5340,7 +5339,7 @@
         <v>11529.411764705899</v>
       </c>
     </row>
-    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>48</v>
       </c>
@@ -5363,7 +5362,7 @@
         <v>50778.333333333299</v>
       </c>
     </row>
-    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
         <v>48</v>
       </c>
@@ -5386,7 +5385,7 @@
         <v>264981.8</v>
       </c>
     </row>
-    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>48</v>
       </c>
@@ -5409,7 +5408,7 @@
         <v>185494.23076923101</v>
       </c>
     </row>
-    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>48</v>
       </c>
@@ -5432,7 +5431,7 @@
         <v>444018.78571428597</v>
       </c>
     </row>
-    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>48</v>
       </c>
@@ -5455,7 +5454,7 @@
         <v>235621.76923076899</v>
       </c>
     </row>
-    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>48</v>
       </c>
@@ -5478,7 +5477,7 @@
         <v>90565.857142857101</v>
       </c>
     </row>
-    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>48</v>
       </c>
@@ -5501,7 +5500,7 @@
         <v>473600</v>
       </c>
     </row>
-    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>48</v>
       </c>
@@ -5524,7 +5523,7 @@
         <v>461304.34782608697</v>
       </c>
     </row>
-    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
         <v>48</v>
       </c>
@@ -5547,7 +5546,7 @@
         <v>1102882.5454545501</v>
       </c>
     </row>
-    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>48</v>
       </c>
@@ -5570,7 +5569,7 @@
         <v>2298704.5499999998</v>
       </c>
     </row>
-    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>48</v>
       </c>
@@ -5593,7 +5592,7 @@
         <v>2304814</v>
       </c>
     </row>
-    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>48</v>
       </c>
@@ -5616,7 +5615,7 @@
         <v>1338022.5217391299</v>
       </c>
     </row>
-    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>48</v>
       </c>
@@ -5639,7 +5638,7 @@
         <v>1244240.7391304299</v>
       </c>
     </row>
-    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>48</v>
       </c>
@@ -5662,7 +5661,7 @@
         <v>1762445.2</v>
       </c>
     </row>
-    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>48</v>
       </c>
@@ -5685,7 +5684,7 @@
         <v>159454.66666666701</v>
       </c>
     </row>
-    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>48</v>
       </c>
@@ -5708,7 +5707,7 @@
         <v>146678.20000000001</v>
       </c>
     </row>
-    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>48</v>
       </c>
@@ -5731,7 +5730,7 @@
         <v>332135.5625</v>
       </c>
     </row>
-    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>48</v>
       </c>
@@ -5754,7 +5753,7 @@
         <v>435003.84615384601</v>
       </c>
     </row>
-    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
         <v>48</v>
       </c>
@@ -5777,7 +5776,7 @@
         <v>697687.91666666698</v>
       </c>
     </row>
-    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
         <v>48</v>
       </c>
@@ -5800,7 +5799,7 @@
         <v>449076.92307692301</v>
       </c>
     </row>
-    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
         <v>48</v>
       </c>
@@ -5823,7 +5822,7 @@
         <v>381743</v>
       </c>
     </row>
-    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>48</v>
       </c>
@@ -5846,7 +5845,7 @@
         <v>289785.55555555603</v>
       </c>
     </row>
-    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>48</v>
       </c>
@@ -5869,7 +5868,7 @@
         <v>461636.363636364</v>
       </c>
     </row>
-    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>48</v>
       </c>
@@ -5892,7 +5891,7 @@
         <v>238181.818181818</v>
       </c>
     </row>
-    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>48</v>
       </c>
@@ -5915,7 +5914,7 @@
         <v>592409.09090909106</v>
       </c>
     </row>
-    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>48</v>
       </c>
@@ -5938,7 +5937,7 @@
         <v>680454.54545454495</v>
       </c>
     </row>
-    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>48</v>
       </c>
@@ -5961,7 +5960,7 @@
         <v>25555.555555555598</v>
       </c>
     </row>
-    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
         <v>48</v>
       </c>
@@ -5984,7 +5983,7 @@
         <v>90909.090909090897</v>
       </c>
     </row>
-    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>48</v>
       </c>
@@ -6007,7 +6006,7 @@
         <v>249868.727272727</v>
       </c>
     </row>
-    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
         <v>48</v>
       </c>
@@ -6030,7 +6029,7 @@
         <v>547277.818181818</v>
       </c>
     </row>
-    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
         <v>54</v>
       </c>
@@ -6053,7 +6052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>54</v>
       </c>
@@ -6076,7 +6075,7 @@
         <v>35318</v>
       </c>
     </row>
-    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>54</v>
       </c>
@@ -6099,7 +6098,7 @@
         <v>58350</v>
       </c>
     </row>
-    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>54</v>
       </c>
@@ -6122,7 +6121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>54</v>
       </c>
@@ -6145,7 +6144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
         <v>54</v>
       </c>
@@ -6168,7 +6167,7 @@
         <v>22222.222222222201</v>
       </c>
     </row>
-    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
         <v>54</v>
       </c>
@@ -6191,7 +6190,7 @@
         <v>7330</v>
       </c>
     </row>
-    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>54</v>
       </c>
@@ -6214,7 +6213,7 @@
         <v>61222.222222222197</v>
       </c>
     </row>
-    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>54</v>
       </c>
@@ -6237,7 +6236,7 @@
         <v>31666.666666666701</v>
       </c>
     </row>
-    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>54</v>
       </c>
@@ -6260,7 +6259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>54</v>
       </c>
@@ -6283,7 +6282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
         <v>54</v>
       </c>
@@ -6306,7 +6305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
         <v>54</v>
       </c>
@@ -6329,7 +6328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
         <v>54</v>
       </c>
@@ -6352,7 +6351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>54</v>
       </c>
@@ -6375,7 +6374,7 @@
         <v>24166.666666666701</v>
       </c>
     </row>
-    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>54</v>
       </c>
@@ -6398,7 +6397,7 @@
         <v>18181.818181818198</v>
       </c>
     </row>
-    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>54</v>
       </c>
@@ -6421,7 +6420,7 @@
         <v>2511000</v>
       </c>
     </row>
-    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>54</v>
       </c>
@@ -6444,7 +6443,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>54</v>
       </c>
@@ -6467,7 +6466,7 @@
         <v>4681917.3333333302</v>
       </c>
     </row>
-    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>54</v>
       </c>
@@ -6490,7 +6489,7 @@
         <v>8026826.4000000004</v>
       </c>
     </row>
-    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>54</v>
       </c>
@@ -6513,7 +6512,7 @@
         <v>5418400</v>
       </c>
     </row>
-    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>54</v>
       </c>
@@ -6536,7 +6535,7 @@
         <v>5298716.8333333302</v>
       </c>
     </row>
-    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>54</v>
       </c>
@@ -6559,7 +6558,7 @@
         <v>222222.22222222199</v>
       </c>
     </row>
-    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>54</v>
       </c>
@@ -6582,7 +6581,7 @@
         <v>166666.66666666701</v>
       </c>
     </row>
-    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
         <v>54</v>
       </c>
@@ -6605,7 +6604,7 @@
         <v>1281134.8888888899</v>
       </c>
     </row>
-    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
         <v>54</v>
       </c>
@@ -6628,7 +6627,7 @@
         <v>938938.66666666698</v>
       </c>
     </row>
-    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
         <v>54</v>
       </c>
@@ -6651,7 +6650,7 @@
         <v>1406111.1111111101</v>
       </c>
     </row>
-    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
         <v>54</v>
       </c>
@@ -6674,7 +6673,7 @@
         <v>649938.44444444403</v>
       </c>
     </row>
-    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>54</v>
       </c>
@@ -6697,7 +6696,7 @@
         <v>714055.55555555597</v>
       </c>
     </row>
-    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>54</v>
       </c>
@@ -6720,7 +6719,7 @@
         <v>682411.11111111101</v>
       </c>
     </row>
-    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
         <v>54</v>
       </c>
@@ -6743,7 +6742,7 @@
         <v>179600</v>
       </c>
     </row>
-    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
         <v>54</v>
       </c>
@@ -6766,7 +6765,7 @@
         <v>94230.769230769205</v>
       </c>
     </row>
-    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
         <v>54</v>
       </c>
@@ -6789,7 +6788,7 @@
         <v>106027.69230769201</v>
       </c>
     </row>
-    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
         <v>54</v>
       </c>
@@ -6812,7 +6811,7 @@
         <v>583384.61538461503</v>
       </c>
     </row>
-    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
         <v>54</v>
       </c>
@@ -6835,7 +6834,7 @@
         <v>104854.285714286</v>
       </c>
     </row>
-    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
         <v>54</v>
       </c>
@@ -6858,7 +6857,7 @@
         <v>24285.714285714301</v>
       </c>
     </row>
-    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
         <v>54</v>
       </c>
@@ -6881,7 +6880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>54</v>
       </c>
@@ -6904,7 +6903,7 @@
         <v>98571.428571428594</v>
       </c>
     </row>
-    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
         <v>61</v>
       </c>
@@ -6927,7 +6926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
         <v>61</v>
       </c>
@@ -6950,7 +6949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
         <v>61</v>
       </c>
@@ -6973,7 +6972,7 @@
         <v>20719</v>
       </c>
     </row>
-    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
         <v>61</v>
       </c>
@@ -6996,7 +6995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
         <v>61</v>
       </c>
@@ -7019,7 +7018,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
         <v>61</v>
       </c>
@@ -7042,7 +7041,7 @@
         <v>14250</v>
       </c>
     </row>
-    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
         <v>61</v>
       </c>
@@ -7065,7 +7064,7 @@
         <v>15454.5454545455</v>
       </c>
     </row>
-    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
         <v>61</v>
       </c>
@@ -7088,7 +7087,7 @@
         <v>30384.615384615401</v>
       </c>
     </row>
-    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
         <v>61</v>
       </c>
@@ -7111,7 +7110,7 @@
         <v>5357.1428571428596</v>
       </c>
     </row>
-    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
         <v>61</v>
       </c>
@@ -7134,7 +7133,7 @@
         <v>35185.333333333299</v>
       </c>
     </row>
-    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
         <v>61</v>
       </c>
@@ -7157,7 +7156,7 @@
         <v>16153.8461538462</v>
       </c>
     </row>
-    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
         <v>61</v>
       </c>
@@ -7180,7 +7179,7 @@
         <v>76416.666666666701</v>
       </c>
     </row>
-    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
         <v>61</v>
       </c>
@@ -7203,7 +7202,7 @@
         <v>108916.66666666701</v>
       </c>
     </row>
-    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
         <v>61</v>
       </c>
@@ -7226,7 +7225,7 @@
         <v>268750</v>
       </c>
     </row>
-    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
         <v>61</v>
       </c>
@@ -7249,7 +7248,7 @@
         <v>239230.76923076899</v>
       </c>
     </row>
-    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
         <v>61</v>
       </c>
@@ -7272,7 +7271,7 @@
         <v>1713181.81818182</v>
       </c>
     </row>
-    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
         <v>61</v>
       </c>
@@ -7295,7 +7294,7 @@
         <v>493750</v>
       </c>
     </row>
-    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
         <v>61</v>
       </c>
@@ -7318,7 +7317,7 @@
         <v>353846.15384615399</v>
       </c>
     </row>
-    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>61</v>
       </c>
@@ -7341,7 +7340,7 @@
         <v>217923.07692307699</v>
       </c>
     </row>
-    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
         <v>61</v>
       </c>
@@ -7364,7 +7363,7 @@
         <v>3928571.42857143</v>
       </c>
     </row>
-    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
         <v>61</v>
       </c>
@@ -7387,7 +7386,7 @@
         <v>41857.142857142899</v>
       </c>
     </row>
-    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
         <v>61</v>
       </c>
@@ -7410,7 +7409,7 @@
         <v>462042.85714285698</v>
       </c>
     </row>
-    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
         <v>61</v>
       </c>
@@ -7433,7 +7432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>61</v>
       </c>
@@ -7456,7 +7455,7 @@
         <v>283571.42857142899</v>
       </c>
     </row>
-    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>61</v>
       </c>
@@ -7479,7 +7478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
         <v>61</v>
       </c>
@@ -7502,7 +7501,7 @@
         <v>35714.285714285703</v>
       </c>
     </row>
-    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
         <v>61</v>
       </c>
@@ -7525,7 +7524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
         <v>61</v>
       </c>
@@ -7548,7 +7547,7 @@
         <v>501890.84210526297</v>
       </c>
     </row>
-    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>61</v>
       </c>
@@ -7571,7 +7570,7 @@
         <v>467730.52631578897</v>
       </c>
     </row>
-    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
         <v>61</v>
       </c>
@@ -7594,7 +7593,7 @@
         <v>515472.63157894701</v>
       </c>
     </row>
-    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
         <v>61</v>
       </c>
@@ -7617,7 +7616,7 @@
         <v>390350</v>
       </c>
     </row>
-    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
         <v>61</v>
       </c>
@@ -7640,7 +7639,7 @@
         <v>477052.63157894701</v>
       </c>
     </row>
-    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
         <v>61</v>
       </c>
@@ -7663,7 +7662,7 @@
         <v>370032.9</v>
       </c>
     </row>
-    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
         <v>61</v>
       </c>
@@ -7686,7 +7685,7 @@
         <v>685230.83333333302</v>
       </c>
     </row>
-    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
         <v>61</v>
       </c>
@@ -7709,7 +7708,7 @@
         <v>418277.11111111101</v>
       </c>
     </row>
-    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
         <v>61</v>
       </c>
@@ -7732,7 +7731,7 @@
         <v>220865</v>
       </c>
     </row>
-    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
         <v>61</v>
       </c>
@@ -7755,7 +7754,7 @@
         <v>82727.272727272706</v>
       </c>
     </row>
-    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
         <v>61</v>
       </c>
@@ -7778,7 +7777,7 @@
         <v>129272.727272727</v>
       </c>
     </row>
-    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
         <v>61</v>
       </c>
@@ -7801,7 +7800,7 @@
         <v>215363.636363636</v>
       </c>
     </row>
-    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
         <v>61</v>
       </c>
@@ -7824,7 +7823,7 @@
         <v>144000</v>
       </c>
     </row>
-    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
         <v>61</v>
       </c>
@@ -7847,7 +7846,7 @@
         <v>216260.88888888899</v>
       </c>
     </row>
-    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
         <v>61</v>
       </c>
@@ -7870,7 +7869,7 @@
         <v>177111.11111111101</v>
       </c>
     </row>
-    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
         <v>61</v>
       </c>
@@ -7893,7 +7892,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
         <v>61</v>
       </c>
@@ -7916,7 +7915,7 @@
         <v>276488.34999999998</v>
       </c>
     </row>
-    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
         <v>61</v>
       </c>
@@ -7939,7 +7938,7 @@
         <v>373171.5</v>
       </c>
     </row>
-    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
         <v>61</v>
       </c>
@@ -7962,7 +7961,7 @@
         <v>254552.77777777801</v>
       </c>
     </row>
-    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
         <v>61</v>
       </c>
@@ -7985,7 +7984,7 @@
         <v>355285.88235294097</v>
       </c>
     </row>
-    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
         <v>61</v>
       </c>
@@ -8008,7 +8007,7 @@
         <v>710372</v>
       </c>
     </row>
-    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
         <v>61</v>
       </c>
@@ -8031,7 +8030,7 @@
         <v>464289.95</v>
       </c>
     </row>
-    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
         <v>61</v>
       </c>
@@ -8054,7 +8053,7 @@
         <v>725441.5</v>
       </c>
     </row>
-    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
         <v>61</v>
       </c>
@@ -8077,7 +8076,7 @@
         <v>269079.38095238101</v>
       </c>
     </row>
-    <row r="323" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
         <v>61</v>
       </c>
@@ -8100,7 +8099,7 @@
         <v>466687.05882352899</v>
       </c>
     </row>
-    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
         <v>61</v>
       </c>
@@ -8123,7 +8122,7 @@
         <v>112997.352941176</v>
       </c>
     </row>
-    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
         <v>61</v>
       </c>
@@ -8146,7 +8145,7 @@
         <v>171728.94117647101</v>
       </c>
     </row>
-    <row r="326" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
         <v>61</v>
       </c>
@@ -8169,7 +8168,7 @@
         <v>196250</v>
       </c>
     </row>
-    <row r="327" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
         <v>61</v>
       </c>
@@ -8192,7 +8191,7 @@
         <v>390325</v>
       </c>
     </row>
-    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
         <v>61</v>
       </c>
@@ -8215,7 +8214,7 @@
         <v>818933.8125</v>
       </c>
     </row>
-    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
         <v>61</v>
       </c>
@@ -8238,7 +8237,7 @@
         <v>470666.66666666698</v>
       </c>
     </row>
-    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
         <v>61</v>
       </c>
@@ -8261,7 +8260,7 @@
         <v>2452666.6666666698</v>
       </c>
     </row>
-    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
         <v>61</v>
       </c>
@@ -8284,7 +8283,7 @@
         <v>822277.77777777798</v>
       </c>
     </row>
-    <row r="332" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
         <v>61</v>
       </c>
@@ -8307,7 +8306,7 @@
         <v>346705.88235294097</v>
       </c>
     </row>
-    <row r="333" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
         <v>61</v>
       </c>
@@ -8330,7 +8329,7 @@
         <v>1318316.625</v>
       </c>
     </row>
-    <row r="334" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
         <v>61</v>
       </c>
@@ -8353,7 +8352,7 @@
         <v>531478.86666666705</v>
       </c>
     </row>
-    <row r="335" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
         <v>61</v>
       </c>
@@ -8376,7 +8375,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
         <v>61</v>
       </c>
@@ -8399,7 +8398,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
         <v>61</v>
       </c>
@@ -8422,7 +8421,7 @@
         <v>73529.411764705903</v>
       </c>
     </row>
-    <row r="338" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
         <v>61</v>
       </c>
@@ -8445,7 +8444,7 @@
         <v>93125</v>
       </c>
     </row>
-    <row r="339" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
         <v>61</v>
       </c>
@@ -8468,7 +8467,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="340" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
         <v>61</v>
       </c>
@@ -8491,7 +8490,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
         <v>61</v>
       </c>
@@ -8514,7 +8513,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
         <v>61</v>
       </c>
@@ -8537,7 +8536,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="343" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
         <v>61</v>
       </c>
@@ -8560,7 +8559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
         <v>61</v>
       </c>
@@ -8583,7 +8582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
         <v>61</v>
       </c>
@@ -8606,7 +8605,7 @@
         <v>32622.222222222201</v>
       </c>
     </row>
-    <row r="346" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
         <v>61</v>
       </c>
@@ -8629,7 +8628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
         <v>71</v>
       </c>
@@ -8652,7 +8651,7 @@
         <v>53333.333333333299</v>
       </c>
     </row>
-    <row r="348" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
         <v>71</v>
       </c>
@@ -8675,7 +8674,7 @@
         <v>285000</v>
       </c>
     </row>
-    <row r="349" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
         <v>71</v>
       </c>
@@ -8698,7 +8697,7 @@
         <v>381833.33333333302</v>
       </c>
     </row>
-    <row r="350" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
         <v>71</v>
       </c>
@@ -8721,7 +8720,7 @@
         <v>165000</v>
       </c>
     </row>
-    <row r="351" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
         <v>71</v>
       </c>
@@ -8744,7 +8743,7 @@
         <v>630166.66666666698</v>
       </c>
     </row>
-    <row r="352" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
         <v>71</v>
       </c>
@@ -8767,7 +8766,7 @@
         <v>862571.42857142899</v>
       </c>
     </row>
-    <row r="353" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
         <v>71</v>
       </c>
@@ -8790,7 +8789,7 @@
         <v>357562.5</v>
       </c>
     </row>
-    <row r="354" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
         <v>71</v>
       </c>
@@ -8813,7 +8812,7 @@
         <v>232625</v>
       </c>
     </row>
-    <row r="355" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
         <v>71</v>
       </c>
@@ -8836,7 +8835,7 @@
         <v>202003.33333333299</v>
       </c>
     </row>
-    <row r="356" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
         <v>71</v>
       </c>
@@ -8859,7 +8858,7 @@
         <v>57155</v>
       </c>
     </row>
-    <row r="357" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
         <v>71</v>
       </c>
@@ -8882,7 +8881,7 @@
         <v>266296.66666666698</v>
       </c>
     </row>
-    <row r="358" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
         <v>71</v>
       </c>
@@ -8905,7 +8904,7 @@
         <v>242409.285714286</v>
       </c>
     </row>
-    <row r="359" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
         <v>71</v>
       </c>
@@ -8928,7 +8927,7 @@
         <v>179856.25</v>
       </c>
     </row>
-    <row r="360" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
         <v>71</v>
       </c>
@@ -8951,7 +8950,7 @@
         <v>226352.63157894701</v>
       </c>
     </row>
-    <row r="361" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
         <v>71</v>
       </c>
@@ -8974,7 +8973,7 @@
         <v>1453229.8095238099</v>
       </c>
     </row>
-    <row r="362" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
         <v>71</v>
       </c>
@@ -8997,7 +8996,7 @@
         <v>170333.33333333299</v>
       </c>
     </row>
-    <row r="363" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
         <v>71</v>
       </c>
@@ -9020,7 +9019,7 @@
         <v>505666.66666666698</v>
       </c>
     </row>
-    <row r="364" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
         <v>71</v>
       </c>
@@ -9043,7 +9042,7 @@
         <v>707893.11111111101</v>
       </c>
     </row>
-    <row r="365" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
         <v>71</v>
       </c>
@@ -9066,7 +9065,7 @@
         <v>331666.66666666698</v>
       </c>
     </row>
-    <row r="366" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
         <v>71</v>
       </c>
@@ -9089,7 +9088,7 @@
         <v>292712</v>
       </c>
     </row>
-    <row r="367" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
         <v>71</v>
       </c>
@@ -9112,7 +9111,7 @@
         <v>279218.181818182</v>
       </c>
     </row>
-    <row r="368" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
         <v>71</v>
       </c>
@@ -9135,7 +9134,7 @@
         <v>340618.181818182</v>
       </c>
     </row>
-    <row r="369" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
         <v>71</v>
       </c>
@@ -9158,7 +9157,7 @@
         <v>406909.090909091</v>
       </c>
     </row>
-    <row r="370" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
         <v>71</v>
       </c>
@@ -9181,7 +9180,7 @@
         <v>552909.09090909106</v>
       </c>
     </row>
-    <row r="371" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
         <v>71</v>
       </c>
@@ -9204,7 +9203,7 @@
         <v>244889.92857142899</v>
       </c>
     </row>
-    <row r="372" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
         <v>71</v>
       </c>
@@ -9227,7 +9226,7 @@
         <v>343581.03571428597</v>
       </c>
     </row>
-    <row r="373" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
         <v>71</v>
       </c>
@@ -9250,7 +9249,7 @@
         <v>346496.74074074102</v>
       </c>
     </row>
-    <row r="374" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
         <v>71</v>
       </c>
@@ -9273,7 +9272,7 @@
         <v>191293.84615384601</v>
       </c>
     </row>
-    <row r="375" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
         <v>71</v>
       </c>
@@ -9296,7 +9295,7 @@
         <v>837736.64</v>
       </c>
     </row>
-    <row r="376" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
         <v>71</v>
       </c>
@@ -9319,7 +9318,7 @@
         <v>519492.85714285698</v>
       </c>
     </row>
-    <row r="377" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
         <v>71</v>
       </c>
@@ -9342,7 +9341,7 @@
         <v>689117.24137931003</v>
       </c>
     </row>
-    <row r="378" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
         <v>71</v>
       </c>
@@ -9365,7 +9364,7 @@
         <v>685307.13333333295</v>
       </c>
     </row>
-    <row r="379" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
         <v>71</v>
       </c>
@@ -9388,7 +9387,7 @@
         <v>2696179</v>
       </c>
     </row>
-    <row r="380" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
         <v>71</v>
       </c>
@@ -9411,7 +9410,7 @@
         <v>2715223</v>
       </c>
     </row>
-    <row r="381" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="s">
         <v>71</v>
       </c>
@@ -9434,7 +9433,7 @@
         <v>1844488.36363636</v>
       </c>
     </row>
-    <row r="382" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
         <v>71</v>
       </c>
@@ -9457,7 +9456,7 @@
         <v>9360200.75</v>
       </c>
     </row>
-    <row r="383" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
         <v>71</v>
       </c>
@@ -9480,7 +9479,7 @@
         <v>8583883.1666666698</v>
       </c>
     </row>
-    <row r="384" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
         <v>71</v>
       </c>
@@ -9503,7 +9502,7 @@
         <v>6870742.0769230798</v>
       </c>
     </row>
-    <row r="385" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
         <v>71</v>
       </c>
@@ -9526,7 +9525,7 @@
         <v>6728426.9230769202</v>
       </c>
     </row>
-    <row r="386" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A386" s="2" t="s">
         <v>71</v>
       </c>
@@ -9549,7 +9548,7 @@
         <v>61780696.727272697</v>
       </c>
     </row>
-    <row r="387" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
         <v>71</v>
       </c>
@@ -9572,7 +9571,7 @@
         <v>1693794.1612903201</v>
       </c>
     </row>
-    <row r="388" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
         <v>71</v>
       </c>
@@ -9595,7 +9594,7 @@
         <v>1465370.9677419399</v>
       </c>
     </row>
-    <row r="389" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
         <v>71</v>
       </c>
@@ -9618,7 +9617,7 @@
         <v>932959.15151515102</v>
       </c>
     </row>
-    <row r="390" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
         <v>71</v>
       </c>
@@ -9641,7 +9640,7 @@
         <v>1245854.6764705901</v>
       </c>
     </row>
-    <row r="391" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
         <v>71</v>
       </c>
@@ -9664,7 +9663,7 @@
         <v>1072247.8787878801</v>
       </c>
     </row>
-    <row r="392" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
         <v>71</v>
       </c>
@@ -9687,7 +9686,7 @@
         <v>1391055</v>
       </c>
     </row>
-    <row r="393" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
         <v>71</v>
       </c>
@@ -9710,7 +9709,7 @@
         <v>783386.66666666698</v>
       </c>
     </row>
-    <row r="394" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
         <v>71</v>
       </c>
@@ -9733,7 +9732,7 @@
         <v>1347976.4516129</v>
       </c>
     </row>
-    <row r="395" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
         <v>71</v>
       </c>
@@ -9756,7 +9755,7 @@
         <v>432253.6</v>
       </c>
     </row>
-    <row r="396" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
         <v>71</v>
       </c>
@@ -9779,7 +9778,7 @@
         <v>189245</v>
       </c>
     </row>
-    <row r="397" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
         <v>71</v>
       </c>
@@ -9802,7 +9801,7 @@
         <v>184800</v>
       </c>
     </row>
-    <row r="398" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
         <v>71</v>
       </c>
@@ -9825,7 +9824,7 @@
         <v>137350</v>
       </c>
     </row>
-    <row r="399" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
         <v>71</v>
       </c>
@@ -9848,7 +9847,7 @@
         <v>187300</v>
       </c>
     </row>
-    <row r="400" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
         <v>71</v>
       </c>
@@ -9871,7 +9870,7 @@
         <v>101355.952380952</v>
       </c>
     </row>
-    <row r="401" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
         <v>71</v>
       </c>
@@ -9894,7 +9893,7 @@
         <v>115238.095238095</v>
       </c>
     </row>
-    <row r="402" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
         <v>71</v>
       </c>
@@ -9918,13 +9917,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G402" xr:uid="{133FDDBA-F32F-4CCF-AF19-0FCBF20D9188}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="會計資訊系"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
